--- a/results/04_final_refined_daily_hydroclimate_data/209/Dry_bulb_temp_15h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Dry_bulb_temp_15h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Dry_bulb_temp_15h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -553,8 +550,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>28.6</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -581,8 +578,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>4</v>
+      <c r="D14">
+        <v>25.5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -595,8 +592,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>30.1</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -624,7 +621,7 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -763,8 +760,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="D27">
+        <v>30.4</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -791,8 +788,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -805,8 +802,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
-        <v>4</v>
+      <c r="D30">
+        <v>30.8</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -819,8 +816,8 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
+      <c r="D31">
+        <v>24.7</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -833,8 +830,8 @@
       <c r="C32">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
-        <v>4</v>
+      <c r="D32">
+        <v>22.6</v>
       </c>
     </row>
   </sheetData>
